--- a/Dictionary/Mapping.xlsx
+++ b/Dictionary/Mapping.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Moderator\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\H\iot_app\coctimer\Dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72307260-034B-42E5-9A4B-AEA17160E048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EBB86F-4544-4BE6-9B00-135111345B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{73A4CEDB-1190-452B-8471-502024852691}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12600" xr2:uid="{73A4CEDB-1190-452B-8471-502024852691}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="908">
   <si>
     <t>ID</t>
   </si>
@@ -7639,6 +7639,835 @@
   </si>
   <si>
     <t>@override String get separatorDots =&gt;</t>
+  </si>
+  <si>
+    <t>1000019:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">settingsTitle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"■ TIME CONTROLLER"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">settingsGroupTitlePrefix </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"AUTO SWITCH TO "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">settingsGroupTitleSuffix </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>" AT"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">settingsTo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"to"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">settingsAnd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"and"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">settingsBtnAdd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"[ ADD ]"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">settingsGlobalDesc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"&gt; OUTSIDE THESE HOURS, APP WILL: "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">settingsActionNone </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SILENT"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">settingsActionSystem </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"NOTIFY"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">settingsActionFullscreen </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"ALARM"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">labelPickStart </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Start Time"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">labelPickEnd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"End Time"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">errorOverlap </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"ERROR: This time range overlaps with an existing rule!"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">@override </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">String </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF8E6D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">get </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">btnDeleteRule </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"[ DEL ]"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8550,7 +9379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F40EBD-29F1-4C46-8658-290CA80DFCD5}">
-  <dimension ref="A1:C286"/>
+  <dimension ref="A1:C287"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -10618,7 +11447,7 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>454</v>
+        <v>893</v>
       </c>
       <c r="B198" t="s">
         <v>455</v>
@@ -10629,953 +11458,953 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B199" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C199" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B200" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C200" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B201" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C201" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B202" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C202" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B203" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C203" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B204" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C204" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B205" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C205" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B206" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C206" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B207" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C207" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B208" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C208" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B209" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C209" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B210" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C210" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B211" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C211" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B212" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C212" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B213" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C213" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B214" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C214" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B215" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C215" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B216" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C216" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B217" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C217" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B218" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C218" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B219" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C219" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B220" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C220" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B221" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C221" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B222" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C222" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B223" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C223" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B224" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C224" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B225" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C225" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B226" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C226" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B227" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C227" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B228" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C228" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B229" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C229" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B230" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C230" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B231" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C231" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B232" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C232" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B233" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C233" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B234" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C234" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B235" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C235" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B236" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C236" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B237" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C237" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B238" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C238" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B239" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C239" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B240" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C240" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B241" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C241" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B242" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C242" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B243" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C243" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B244" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C244" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B245" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C245" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B246" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C246" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B247" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C247" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B248" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C248" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B249" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C249" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B250" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C250" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B251" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C251" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B252" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C252" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B253" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C253" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B254" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C254" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B255" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C255" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B256" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C256" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B257" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C257" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B258" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C258" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B259" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C259" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B260" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C260" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B261" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C261" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B262" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C262" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B263" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C263" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B264" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C264" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B265" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C265" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B266" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C266" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B267" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C267" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B268" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C268" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B269" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C269" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B270" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C270" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B271" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C271" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B272" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C272" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B273" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C273" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B274" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C274" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B275" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C275" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B276" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C276" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B277" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C277" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B278" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C278" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B279" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C279" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B280" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C280" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B281" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C281" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B282" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C282" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B283" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C283" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B284" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C284" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B285" t="s">
         <v>709</v>
@@ -11586,12 +12415,23 @@
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
+        <v>711</v>
+      </c>
+      <c r="B286" t="s">
+        <v>709</v>
+      </c>
+      <c r="C286" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287" t="s">
         <v>712</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B287" t="s">
         <v>713</v>
       </c>
-      <c r="C286" t="s">
+      <c r="C287" t="s">
         <v>714</v>
       </c>
     </row>
@@ -11602,7 +12442,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D554DEE9-F5FE-496B-95D8-9BF128C6925A}">
-  <dimension ref="A1:B95"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="65.59765625" customWidth="1"/>
@@ -12168,7 +13008,7 @@
         <v>725</v>
       </c>
       <c r="B68" t="str">
-        <f t="shared" ref="B68:B95" si="1">LEFT(A68,FIND("=&gt;",A68)+1)</f>
+        <f t="shared" ref="B68:B110" si="1">LEFT(A68,FIND("=&gt;",A68)+1)</f>
         <v>@override String get statusWorkingSuffix =&gt;</v>
       </c>
     </row>
@@ -12395,6 +13235,132 @@
       <c r="B95" t="str">
         <f t="shared" si="1"/>
         <v>@override String get welcomeNotificationBody =&gt;</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="B97" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get settingsTitle =&gt;</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B98" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get settingsGroupTitlePrefix =&gt;</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="B99" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get settingsGroupTitleSuffix =&gt;</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="B100" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get settingsTo =&gt;</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="B101" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get settingsAnd =&gt;</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="B102" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get settingsBtnAdd =&gt;</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B103" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get settingsGlobalDesc =&gt;</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="B104" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get settingsActionNone =&gt;</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B105" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get settingsActionSystem =&gt;</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B106" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get settingsActionFullscreen =&gt;</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="B107" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get labelPickStart =&gt;</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="B108" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get labelPickEnd =&gt;</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="B109" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get errorOverlap =&gt;</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="B110" t="str">
+        <f t="shared" si="1"/>
+        <v>@override String get btnDeleteRule =&gt;</v>
       </c>
     </row>
   </sheetData>
